--- a/grupos/3ARHM - Estadisticos 20241.xlsx
+++ b/grupos/3ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="158">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -239,21 +239,27 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -287,9 +293,6 @@
     <t>MATA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
@@ -323,6 +326,9 @@
     <t>XALAMIHUA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -365,9 +371,6 @@
     <t>CANSECO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>TREJO</t>
   </si>
   <si>
@@ -395,19 +398,25 @@
     <t>FIGUEROA</t>
   </si>
   <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MELANIE YARETZI</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
   </si>
   <si>
     <t>ARIADNA</t>
@@ -1028,28 +1037,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1105,7 +1114,7 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1129,28 +1138,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1177,22 +1186,22 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>8</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF5">
         <v>8</v>
@@ -1230,28 +1239,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1281,13 +1290,13 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>10</v>
@@ -1296,7 +1305,7 @@
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1307,7 +1316,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1331,28 +1340,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1379,25 +1388,25 @@
         <v>-1</v>
       </c>
       <c r="Z7">
+        <v>10</v>
+      </c>
+      <c r="AA7">
+        <v>9</v>
+      </c>
+      <c r="AB7">
+        <v>9</v>
+      </c>
+      <c r="AC7">
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <v>9</v>
+      </c>
+      <c r="AE7">
         <v>6</v>
       </c>
-      <c r="AA7">
-        <v>7</v>
-      </c>
-      <c r="AB7">
-        <v>9</v>
-      </c>
-      <c r="AC7">
-        <v>9</v>
-      </c>
-      <c r="AD7">
-        <v>8</v>
-      </c>
-      <c r="AE7">
-        <v>7</v>
-      </c>
       <c r="AF7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1432,28 +1441,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1480,7 +1489,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1492,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="AD8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE8">
         <v>10</v>
@@ -1533,28 +1542,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1584,10 +1593,10 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -1596,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>8</v>
@@ -1634,28 +1643,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1685,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1700,7 +1709,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>-1</v>
@@ -1735,28 +1744,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1786,10 +1795,10 @@
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1801,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="AF11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG11">
         <v>-1</v>
@@ -1836,28 +1845,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1887,13 +1896,13 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD12">
         <v>9</v>
@@ -1902,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1937,28 +1946,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1985,22 +1994,22 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13">
         <v>7</v>
@@ -2038,28 +2047,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2086,10 +2095,10 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -2104,7 +2113,7 @@
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG14">
         <v>-1</v>
@@ -2115,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -2139,28 +2148,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2187,25 +2196,25 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -2240,28 +2249,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2291,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16">
         <v>10</v>
@@ -2306,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG16">
         <v>-1</v>
@@ -2341,28 +2350,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2392,10 +2401,10 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2404,7 +2413,7 @@
         <v>7</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
         <v>7</v>
@@ -2418,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2442,28 +2451,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2490,7 +2499,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2499,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD18">
         <v>8</v>
       </c>
       <c r="AE18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2543,28 +2552,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2594,10 +2603,10 @@
         <v>10</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2620,7 +2629,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2644,28 +2653,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2692,25 +2701,25 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE20">
         <v>5</v>
       </c>
       <c r="AF20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>-1</v>
@@ -2745,28 +2754,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2793,10 +2802,10 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2846,28 +2855,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2897,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2912,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2923,7 +2932,7 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2947,28 +2956,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2995,13 +3004,13 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -3010,7 +3019,7 @@
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF23">
         <v>7</v>
@@ -3048,28 +3057,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3099,13 +3108,13 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD24">
         <v>8</v>
@@ -3149,28 +3158,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3200,22 +3209,22 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>9</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE25">
         <v>5</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>-1</v>
@@ -3226,7 +3235,7 @@
         <v>36</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -3250,28 +3259,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3301,7 +3310,7 @@
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -3313,7 +3322,7 @@
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26">
         <v>6</v>
@@ -3351,28 +3360,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3402,16 +3411,16 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE27">
         <v>10</v>
@@ -3452,28 +3461,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3500,10 +3509,10 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3512,13 +3521,13 @@
         <v>9</v>
       </c>
       <c r="AD28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG28">
         <v>-1</v>
@@ -3553,28 +3562,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3610,10 +3619,10 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -3654,28 +3663,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3705,13 +3714,13 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD30">
         <v>7</v>
@@ -3720,7 +3729,7 @@
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG30">
         <v>-1</v>
@@ -3755,28 +3764,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3806,7 +3815,7 @@
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3856,28 +3865,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3904,25 +3913,25 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32">
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG32">
         <v>-1</v>
@@ -3933,7 +3942,7 @@
         <v>43</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>9</v>
@@ -3957,28 +3966,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -4005,10 +4014,10 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -4017,7 +4026,7 @@
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE33">
         <v>10</v>
@@ -4043,7 +4052,7 @@
         <v>5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -4058,28 +4067,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -4109,22 +4118,22 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>5</v>
       </c>
       <c r="AD34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE34">
         <v>5</v>
       </c>
       <c r="AF34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG34">
         <v>-1</v>
@@ -4159,28 +4168,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4207,19 +4216,19 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE35">
         <v>5</v>
@@ -4236,52 +4245,52 @@
         <v>46</v>
       </c>
       <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>7</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+      <c r="H36">
+        <v>8</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="K36">
+        <v>10</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+      <c r="M36">
         <v>6</v>
       </c>
-      <c r="C36">
-        <v>9</v>
-      </c>
-      <c r="D36">
-        <v>8</v>
-      </c>
-      <c r="E36">
-        <v>7</v>
-      </c>
-      <c r="F36">
-        <v>7</v>
-      </c>
-      <c r="G36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>8</v>
-      </c>
-      <c r="I36">
-        <v>10</v>
-      </c>
-      <c r="J36">
-        <v>-1</v>
-      </c>
-      <c r="K36">
-        <v>-1</v>
-      </c>
-      <c r="L36">
-        <v>-1</v>
-      </c>
-      <c r="M36">
-        <v>-1</v>
-      </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4308,25 +4317,25 @@
         <v>-1</v>
       </c>
       <c r="Z36">
+        <v>10</v>
+      </c>
+      <c r="AA36">
+        <v>10</v>
+      </c>
+      <c r="AB36">
+        <v>7</v>
+      </c>
+      <c r="AC36">
+        <v>7</v>
+      </c>
+      <c r="AD36">
         <v>6</v>
       </c>
-      <c r="AA36">
-        <v>9</v>
-      </c>
-      <c r="AB36">
-        <v>8</v>
-      </c>
-      <c r="AC36">
-        <v>7</v>
-      </c>
-      <c r="AD36">
-        <v>7</v>
-      </c>
       <c r="AE36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG36">
         <v>-1</v>
@@ -4361,28 +4370,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4412,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -4462,28 +4471,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4943,10 +4952,10 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4967,10 +4976,10 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -5020,7 +5029,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -5044,7 +5053,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -5162,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -5186,7 +5195,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -5396,7 +5405,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5405,10 +5414,10 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5420,7 +5429,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5429,10 +5438,10 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -5713,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5737,7 +5746,7 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -5781,10 +5790,10 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="M18">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -5805,10 +5814,10 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U18">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5861,7 +5870,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -5870,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5885,7 +5894,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5894,7 +5903,7 @@
         <v>100</v>
       </c>
       <c r="X19">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -5932,7 +5941,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L20">
         <v>97.2</v>
@@ -5944,10 +5953,10 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>77.8</v>
+        <v>84.8</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5956,7 +5965,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T20">
         <v>97.2</v>
@@ -5968,10 +5977,10 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>77.8</v>
+        <v>84.8</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -6169,7 +6178,7 @@
         <v>97.2</v>
       </c>
       <c r="M23">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -6178,7 +6187,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -6193,7 +6202,7 @@
         <v>97.2</v>
       </c>
       <c r="U23">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -6202,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -6394,10 +6403,10 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -6406,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -6418,10 +6427,10 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6430,7 +6439,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6551,10 +6560,10 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M28">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -6575,10 +6584,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U28">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6637,7 +6646,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6661,7 +6670,7 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X29">
         <v>100</v>
@@ -6705,7 +6714,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6729,7 +6738,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -6856,10 +6865,10 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L32">
-        <v>88.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -6880,10 +6889,10 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T32">
-        <v>88.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -6995,7 +7004,7 @@
         <v>58.3</v>
       </c>
       <c r="F34">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>88.90000000000001</v>
@@ -7013,16 +7022,16 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>83.3</v>
+        <v>90.3</v>
       </c>
       <c r="M34">
-        <v>58.3</v>
+        <v>77.3</v>
       </c>
       <c r="N34">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -7037,16 +7046,16 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>83.3</v>
+        <v>90.3</v>
       </c>
       <c r="U34">
-        <v>58.3</v>
+        <v>77.3</v>
       </c>
       <c r="V34">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="W34">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X34">
         <v>100</v>
@@ -7090,7 +7099,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -7099,10 +7108,10 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -7114,7 +7123,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -7123,10 +7132,10 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y35">
         <v>100</v>
@@ -7170,13 +7179,13 @@
         <v>100</v>
       </c>
       <c r="M36">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N36">
         <v>100</v>
       </c>
       <c r="O36">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -7194,13 +7203,13 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V36">
         <v>100</v>
       </c>
       <c r="W36">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X36">
         <v>100</v>
@@ -7330,7 +7339,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -7354,7 +7363,7 @@
         <v>100</v>
       </c>
       <c r="W38">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X38">
         <v>100</v>
@@ -7467,7 +7476,7 @@
         <v>11.4</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7487,19 +7496,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="G4" s="2">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7519,19 +7528,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="G5" s="2">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7542,7 +7551,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -7551,19 +7560,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>91.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7574,7 +7583,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -7583,19 +7592,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7606,7 +7615,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -7615,19 +7624,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7647,19 +7656,19 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7709,7 +7718,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7741,22 +7750,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920083</v>
+        <v>23330051920357</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7764,16 +7773,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920083</v>
+        <v>23330051920357</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -7787,22 +7796,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920065</v>
+        <v>23330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7810,16 +7819,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920065</v>
+        <v>23330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -7833,33 +7842,33 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920048</v>
+        <v>23330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920049</v>
+        <v>23330051920065</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
         <v>103</v>
@@ -7879,10 +7888,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920050</v>
+        <v>23330051920048</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>104</v>
@@ -7902,10 +7911,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920053</v>
+        <v>23330051920049</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>105</v>
@@ -7925,10 +7934,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920227</v>
+        <v>23330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
         <v>106</v>
@@ -7948,13 +7957,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920054</v>
+        <v>23330051920083</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>132</v>
@@ -7971,13 +7980,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920055</v>
+        <v>23330051920053</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -7994,13 +8003,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920056</v>
+        <v>23330051920227</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
         <v>134</v>
@@ -8017,13 +8026,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920057</v>
+        <v>23330051920054</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -8040,7 +8049,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920058</v>
+        <v>23330051920055</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
@@ -8063,7 +8072,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920246</v>
+        <v>23330051920056</v>
       </c>
       <c r="B16" t="s">
         <v>84</v>
@@ -8086,13 +8095,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920060</v>
+        <v>23330051920057</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -8109,13 +8118,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920061</v>
+        <v>23330051920058</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -8132,13 +8141,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920062</v>
+        <v>23330051920246</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -8155,10 +8164,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920307</v>
+        <v>23330051920060</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
         <v>114</v>
@@ -8178,10 +8187,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920063</v>
+        <v>23330051920061</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
@@ -8201,13 +8210,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920064</v>
+        <v>23330051920062</v>
       </c>
       <c r="B22" t="s">
         <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -8224,7 +8233,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920260</v>
+        <v>23330051920307</v>
       </c>
       <c r="B23" t="s">
         <v>90</v>
@@ -8247,13 +8256,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920066</v>
+        <v>23330051920063</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -8270,13 +8279,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920067</v>
+        <v>23330051920064</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -8293,13 +8302,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920068</v>
+        <v>23330051920260</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -8316,13 +8325,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920069</v>
+        <v>23330051920066</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -8339,13 +8348,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920070</v>
+        <v>23330051920067</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -8362,13 +8371,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920330</v>
+        <v>23330051920068</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -8385,13 +8394,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920272</v>
+        <v>23330051920069</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -8408,13 +8417,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920073</v>
+        <v>23330051920070</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -8431,13 +8440,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920074</v>
+        <v>23330051920330</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -8454,13 +8463,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920075</v>
+        <v>23330051920272</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -8472,6 +8481,75 @@
         <v>61</v>
       </c>
       <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920073</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920074</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920075</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20241.xlsx
+++ b/grupos/3ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -239,6 +239,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>OLMOS</t>
   </si>
   <si>
@@ -254,6 +257,9 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -267,6 +273,9 @@
   </si>
   <si>
     <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
@@ -6736,7 +6745,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6768,22 +6777,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920263</v>
+        <v>23330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6791,22 +6800,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920263</v>
+        <v>23330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6814,16 +6823,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -6837,16 +6846,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -6860,22 +6869,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920357</v>
+        <v>23330051920263</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6883,13 +6892,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920259</v>
+        <v>23330051920263</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -6906,13 +6915,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920065</v>
+        <v>23330051920072</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
@@ -6924,6 +6933,98 @@
         <v>61</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920072</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920357</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920065</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20241.xlsx
+++ b/grupos/3ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -209,10 +209,13 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>
@@ -221,9 +224,6 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -242,52 +242,34 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>IVONNE ERIMAR</t>
   </si>
   <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
     <t>NATALIA</t>
   </si>
   <si>
     <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MELANIE YARETZI</t>
   </si>
   <si>
     <t>DENISSE</t>
@@ -838,19 +820,19 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -927,19 +909,19 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1016,19 +998,19 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1105,19 +1087,19 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1194,19 +1176,19 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1283,19 +1265,19 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1372,19 +1354,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1396,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1461,19 +1443,19 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1550,19 +1532,19 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1639,19 +1621,19 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1660,19 +1642,19 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1728,19 +1710,19 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1817,19 +1799,19 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1906,19 +1888,19 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1995,19 +1977,19 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2028,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2084,19 +2066,19 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2105,7 +2087,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2114,10 +2096,10 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2173,19 +2155,19 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2262,19 +2244,19 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2289,13 +2271,13 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2351,19 +2333,19 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2375,7 +2357,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2440,19 +2422,19 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2529,19 +2511,19 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2556,13 +2538,13 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2618,19 +2600,19 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2707,19 +2689,19 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2796,19 +2778,19 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2817,19 +2799,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>6</v>
@@ -2885,19 +2867,19 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2918,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -2974,19 +2956,19 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2995,7 +2977,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3063,19 +3045,19 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3152,19 +3134,19 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3241,19 +3223,19 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3330,19 +3312,19 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3360,10 +3342,10 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3419,19 +3401,19 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3508,19 +3490,19 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3529,19 +3511,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>5</v>
@@ -3597,19 +3579,19 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3618,19 +3600,19 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z35">
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -3686,19 +3668,19 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3719,7 +3701,7 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -3775,19 +3757,19 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3864,19 +3846,19 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -4486,7 +4468,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4693,7 +4675,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4761,7 +4743,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4829,7 +4811,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5033,10 +5015,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.2</v>
+        <v>98.2</v>
       </c>
       <c r="S18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5104,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5166,10 +5148,10 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R20">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5373,10 +5355,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>97.2</v>
+        <v>98.2</v>
       </c>
       <c r="S23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5571,13 +5553,13 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R26">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5713,10 +5695,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S28">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -5849,7 +5831,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5982,10 +5964,10 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R32">
-        <v>93.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6121,10 +6103,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>90.3</v>
+        <v>84.8</v>
       </c>
       <c r="S34">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -6189,7 +6171,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6257,10 +6239,10 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S36">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6526,7 +6508,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6535,19 +6517,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6558,7 +6540,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6567,19 +6549,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6590,7 +6572,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6599,19 +6581,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6622,7 +6604,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6631,19 +6613,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6654,7 +6636,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -6675,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6745,7 +6727,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6783,16 +6765,16 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6806,16 +6788,16 @@
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6829,16 +6811,16 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6846,22 +6828,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920071</v>
+        <v>23330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6869,22 +6851,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920263</v>
+        <v>23330051920072</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6892,22 +6874,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920263</v>
+        <v>23330051920357</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6915,16 +6897,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920072</v>
+        <v>23330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6933,98 +6915,6 @@
         <v>61</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920072</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920357</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920259</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920065</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20241.xlsx
+++ b/grupos/3ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -203,15 +203,15 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -242,37 +242,10 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
   </si>
 </sst>
 </file>
@@ -835,10 +808,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -924,10 +897,10 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -945,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1013,10 +986,10 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1102,10 +1075,10 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1123,10 +1096,10 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1191,10 +1164,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1280,10 +1253,10 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1369,10 +1342,10 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1458,10 +1431,10 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1547,10 +1520,10 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1636,10 +1609,10 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1657,10 +1630,10 @@
         <v>7</v>
       </c>
       <c r="AB13">
+        <v>7</v>
+      </c>
+      <c r="AC13">
         <v>6</v>
-      </c>
-      <c r="AC13">
-        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1725,10 +1698,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1814,10 +1787,10 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1835,7 +1808,7 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1903,10 +1876,10 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1992,10 +1965,10 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2081,10 +2054,10 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2102,10 +2075,10 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2170,10 +2143,10 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2259,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2280,10 +2253,10 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2348,10 +2321,10 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2437,10 +2410,10 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2461,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2526,10 +2499,10 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2615,10 +2588,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2704,10 +2677,10 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2725,7 +2698,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2793,10 +2766,10 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2814,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2882,10 +2855,10 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2971,10 +2944,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2992,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3060,10 +3033,10 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3149,10 +3122,10 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3173,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3238,10 +3211,10 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3327,10 +3300,10 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3348,7 +3321,7 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>7</v>
@@ -3416,10 +3389,10 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3505,10 +3478,10 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3526,10 +3499,10 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3594,10 +3567,10 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3615,10 +3588,10 @@
         <v>7</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3683,10 +3656,10 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3704,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="AB36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC36">
         <v>7</v>
@@ -3772,10 +3745,10 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3861,10 +3834,10 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -4075,7 +4048,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4143,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4208,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4276,10 +4249,10 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V7">
-        <v>97.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4344,10 +4317,10 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4412,10 +4385,10 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4483,7 +4456,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4551,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4619,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4684,10 +4657,10 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>87.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V13">
-        <v>95.5</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4755,7 +4728,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4823,7 +4796,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4888,10 +4861,10 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4956,10 +4929,10 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5024,10 +4997,10 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5095,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>97.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5160,10 +5133,10 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>84.8</v>
+        <v>87.5</v>
       </c>
       <c r="V20">
-        <v>97.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5231,7 +5204,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5299,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5367,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>97.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5432,10 +5405,10 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5500,10 +5473,10 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5568,10 +5541,10 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5636,10 +5609,10 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5704,10 +5677,10 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V28">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5772,10 +5745,10 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5843,7 +5816,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5908,10 +5881,10 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V31">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5976,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6047,7 +6020,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6112,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V34">
-        <v>100</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6180,10 +6153,10 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V35">
-        <v>97.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6248,10 +6221,10 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V36">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6319,7 +6292,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6384,10 +6357,10 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V38">
-        <v>100</v>
+        <v>87.7</v>
       </c>
     </row>
   </sheetData>
@@ -6444,7 +6417,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -6453,19 +6426,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>88.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6485,19 +6458,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6508,7 +6481,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6517,16 +6490,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>8.9</v>
@@ -6727,7 +6700,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6765,156 +6738,18 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920071</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920071</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920072</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920072</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920357</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920065</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
